--- a/tutti-qc-assayprocess/Excel-data/100526061102&200526061102_260620.xlsx
+++ b/tutti-qc-assayprocess/Excel-data/100526061102&200526061102_260620.xlsx
@@ -786,7 +786,11 @@
       <c r="K2" s="36" t="n"/>
       <c r="L2" s="36" t="n"/>
       <c r="M2" s="36" t="n"/>
-      <c r="N2" s="35" t="n"/>
+      <c r="N2" s="35" t="inlineStr">
+        <is>
+          <t>TMQP26F003</t>
+        </is>
+      </c>
       <c r="O2" s="35" t="n"/>
       <c r="P2" s="36" t="n"/>
       <c r="Q2" s="36" t="n"/>
@@ -799,7 +803,11 @@
           <t>Product Code (REF)</t>
         </is>
       </c>
-      <c r="D3" s="36" t="n"/>
+      <c r="D3" s="36" t="inlineStr">
+        <is>
+          <t>905-112</t>
+        </is>
+      </c>
       <c r="E3" s="36" t="n"/>
       <c r="F3" s="36" t="n"/>
       <c r="G3" s="36" t="n"/>
@@ -834,7 +842,11 @@
       <c r="E4" s="36" t="n"/>
       <c r="F4" s="36" t="n"/>
       <c r="G4" s="36" t="n"/>
-      <c r="H4" s="35" t="n"/>
+      <c r="H4" s="35" t="inlineStr">
+        <is>
+          <t>1-000005-26061102</t>
+        </is>
+      </c>
       <c r="I4" s="35" t="n"/>
       <c r="J4" s="36" t="n"/>
       <c r="K4" s="36" t="n"/>
@@ -857,7 +869,11 @@
           <t>Device FW</t>
         </is>
       </c>
-      <c r="D5" s="36" t="n"/>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Q1H250619013 / Q1H250619026 / Q1H250619034</t>
+        </is>
+      </c>
       <c r="E5" s="36" t="n"/>
       <c r="F5" s="36" t="n"/>
       <c r="G5" s="36" t="n"/>
@@ -867,7 +883,11 @@
       <c r="K5" s="36" t="n"/>
       <c r="L5" s="36" t="n"/>
       <c r="M5" s="36" t="n"/>
-      <c r="N5" s="35" t="n"/>
+      <c r="N5" s="35" t="inlineStr">
+        <is>
+          <t>18:08:54 / 18:10:15 / 18:11:06</t>
+        </is>
+      </c>
       <c r="O5" s="35" t="n"/>
       <c r="P5" s="36" t="n"/>
       <c r="Q5" s="36" t="n"/>
@@ -1107,21 +1127,53 @@
           <t>Beads Lot.</t>
         </is>
       </c>
-      <c r="D21" s="43" t="n"/>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>D:2312614W
+2312614X
+2312614Y</t>
+        </is>
+      </c>
       <c r="E21" s="43" t="n"/>
-      <c r="F21" s="43" t="n"/>
+      <c r="F21" s="43" t="inlineStr">
+        <is>
+          <t>D:2612605Z</t>
+        </is>
+      </c>
       <c r="G21" s="43" t="n"/>
-      <c r="H21" s="43" t="n"/>
+      <c r="H21" s="43" t="inlineStr">
+        <is>
+          <t>D:2852618Y / U:2862618Y</t>
+        </is>
+      </c>
       <c r="I21" s="43" t="n"/>
-      <c r="J21" s="43" t="n"/>
+      <c r="J21" s="43" t="inlineStr">
+        <is>
+          <t>D:2462602Z / U:2952602Z</t>
+        </is>
+      </c>
       <c r="K21" s="43" t="n"/>
-      <c r="L21" s="43" t="n"/>
+      <c r="L21" s="43" t="inlineStr">
+        <is>
+          <t>D:21926151
+21926153
+21926154</t>
+        </is>
+      </c>
       <c r="M21" s="43" t="n"/>
-      <c r="N21" s="43" t="n"/>
+      <c r="N21" s="43" t="inlineStr"/>
       <c r="O21" s="43" t="n"/>
-      <c r="P21" s="43" t="n"/>
+      <c r="P21" s="43" t="inlineStr">
+        <is>
+          <t>D:10326193</t>
+        </is>
+      </c>
       <c r="Q21" s="43" t="n"/>
-      <c r="R21" s="43" t="n"/>
+      <c r="R21" s="43" t="inlineStr">
+        <is>
+          <t>D:2772620Z / U:2782620Z</t>
+        </is>
+      </c>
       <c r="S21" s="43" t="n"/>
       <c r="T21" s="43" t="n"/>
       <c r="U21" s="43" t="n"/>
@@ -1352,36 +1404,52 @@
           <t>CV%</t>
         </is>
       </c>
-      <c r="D26" s="43" t="n">
-        <v>0.34</v>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
       </c>
       <c r="E26" s="43" t="n"/>
-      <c r="F26" s="43" t="n">
-        <v>0.68</v>
+      <c r="F26" s="43" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
       </c>
       <c r="G26" s="43" t="n"/>
-      <c r="H26" s="43" t="n">
-        <v>10.2</v>
+      <c r="H26" s="43" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
       </c>
       <c r="I26" s="43" t="n"/>
-      <c r="J26" s="43" t="n">
-        <v>1.46</v>
+      <c r="J26" s="43" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
       </c>
       <c r="K26" s="43" t="n"/>
-      <c r="L26" s="43" t="n">
-        <v>0.78</v>
+      <c r="L26" s="43" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
       </c>
       <c r="M26" s="43" t="n"/>
-      <c r="N26" s="43" t="n">
-        <v>0.17</v>
+      <c r="N26" s="43" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
       </c>
       <c r="O26" s="43" t="n"/>
-      <c r="P26" s="43" t="n">
-        <v>1.15</v>
+      <c r="P26" s="43" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
       </c>
       <c r="Q26" s="43" t="n"/>
-      <c r="R26" s="43" t="n">
-        <v>0.62</v>
+      <c r="R26" s="43" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
       </c>
       <c r="S26" s="43" t="n"/>
       <c r="T26" s="43" t="n"/>
@@ -1539,36 +1607,52 @@
           <t>CV%</t>
         </is>
       </c>
-      <c r="D29" s="40" t="n">
-        <v>2.41</v>
+      <c r="D29" s="40" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
       </c>
       <c r="E29" s="40" t="n"/>
-      <c r="F29" s="40" t="n">
-        <v>2.46</v>
+      <c r="F29" s="40" t="inlineStr">
+        <is>
+          <t>2.46%</t>
+        </is>
       </c>
       <c r="G29" s="40" t="n"/>
-      <c r="H29" s="40" t="n">
-        <v>24.49</v>
+      <c r="H29" s="40" t="inlineStr">
+        <is>
+          <t>24.49%</t>
+        </is>
       </c>
       <c r="I29" s="40" t="n"/>
-      <c r="J29" s="40" t="n">
-        <v>0.63</v>
+      <c r="J29" s="40" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
       </c>
       <c r="K29" s="40" t="n"/>
-      <c r="L29" s="40" t="n">
-        <v>3.26</v>
+      <c r="L29" s="40" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
       </c>
       <c r="M29" s="40" t="n"/>
-      <c r="N29" s="40" t="n">
-        <v>1.76</v>
+      <c r="N29" s="40" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
       </c>
       <c r="O29" s="40" t="n"/>
-      <c r="P29" s="40" t="n">
-        <v>2.41</v>
+      <c r="P29" s="40" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
       </c>
       <c r="Q29" s="40" t="n"/>
-      <c r="R29" s="40" t="n">
-        <v>5.08</v>
+      <c r="R29" s="40" t="inlineStr">
+        <is>
+          <t>5.08%</t>
+        </is>
       </c>
       <c r="S29" s="40" t="n"/>
       <c r="T29" s="40" t="n"/>
@@ -1726,36 +1810,52 @@
           <t>CV%</t>
         </is>
       </c>
-      <c r="D32" s="43" t="n">
-        <v>0.78</v>
+      <c r="D32" s="43" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
       </c>
       <c r="E32" s="43" t="n"/>
-      <c r="F32" s="43" t="n">
-        <v>1.95</v>
+      <c r="F32" s="43" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
       </c>
       <c r="G32" s="43" t="n"/>
-      <c r="H32" s="43" t="n">
-        <v>12.5</v>
+      <c r="H32" s="43" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
       </c>
       <c r="I32" s="43" t="n"/>
-      <c r="J32" s="43" t="n">
-        <v>0.04</v>
+      <c r="J32" s="43" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
       </c>
       <c r="K32" s="43" t="n"/>
-      <c r="L32" s="43" t="n">
-        <v>0.46</v>
+      <c r="L32" s="43" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
       </c>
       <c r="M32" s="43" t="n"/>
-      <c r="N32" s="43" t="n">
-        <v>8.41</v>
+      <c r="N32" s="43" t="inlineStr">
+        <is>
+          <t>8.41%</t>
+        </is>
       </c>
       <c r="O32" s="43" t="n"/>
-      <c r="P32" s="43" t="n">
-        <v>1.33</v>
+      <c r="P32" s="43" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
       </c>
       <c r="Q32" s="43" t="n"/>
-      <c r="R32" s="43" t="n">
-        <v>1.27</v>
+      <c r="R32" s="43" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
       </c>
       <c r="S32" s="43" t="n"/>
       <c r="T32" s="43" t="n"/>
@@ -1913,36 +2013,52 @@
           <t>CV%</t>
         </is>
       </c>
-      <c r="D35" s="40" t="n">
-        <v>0.4</v>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
       </c>
       <c r="E35" s="40" t="n"/>
-      <c r="F35" s="40" t="n">
-        <v>0.19</v>
+      <c r="F35" s="40" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
       </c>
       <c r="G35" s="40" t="n"/>
-      <c r="H35" s="40" t="n">
-        <v>2.35</v>
+      <c r="H35" s="40" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
       </c>
       <c r="I35" s="40" t="n"/>
-      <c r="J35" s="40" t="n">
-        <v>0</v>
+      <c r="J35" s="40" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
       </c>
       <c r="K35" s="40" t="n"/>
-      <c r="L35" s="40" t="n">
-        <v>0.01</v>
+      <c r="L35" s="40" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
       </c>
       <c r="M35" s="40" t="n"/>
-      <c r="N35" s="40" t="n">
-        <v>0.01</v>
+      <c r="N35" s="40" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
       </c>
       <c r="O35" s="40" t="n"/>
-      <c r="P35" s="40" t="n">
-        <v>0.03</v>
+      <c r="P35" s="40" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
       </c>
       <c r="Q35" s="40" t="n"/>
-      <c r="R35" s="40" t="n">
-        <v>0.61</v>
+      <c r="R35" s="40" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
       </c>
       <c r="S35" s="40" t="n"/>
       <c r="T35" s="40" t="n"/>
@@ -3678,36 +3794,52 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" s="1" t="n"/>
       <c r="D5" s="14" t="n"/>
-      <c r="E5" s="43" t="n">
-        <v>0.08</v>
+      <c r="E5" s="43" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
       </c>
       <c r="F5" s="32" t="n"/>
-      <c r="G5" s="43" t="n">
-        <v>0.1</v>
+      <c r="G5" s="43" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
       </c>
       <c r="H5" s="32" t="n"/>
-      <c r="I5" s="43" t="n">
-        <v>0.1</v>
+      <c r="I5" s="43" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
       </c>
       <c r="J5" s="32" t="n"/>
-      <c r="K5" s="43" t="n">
-        <v>0.1</v>
+      <c r="K5" s="43" t="inlineStr">
+        <is>
+          <t>30 umol/L  or 10%</t>
+        </is>
       </c>
       <c r="L5" s="32" t="n"/>
-      <c r="M5" s="43" t="n">
-        <v>0.08</v>
+      <c r="M5" s="43" t="inlineStr">
+        <is>
+          <t>6 mg/dL or 8%</t>
+        </is>
       </c>
       <c r="N5" s="32" t="n"/>
-      <c r="O5" s="43" t="n">
-        <v>0.3</v>
+      <c r="O5" s="43" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
       </c>
       <c r="P5" s="32" t="n"/>
-      <c r="Q5" s="43" t="n">
-        <v>0.08</v>
+      <c r="Q5" s="43" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
       </c>
       <c r="R5" s="32" t="n"/>
-      <c r="S5" s="43" t="n">
-        <v>0.15</v>
+      <c r="S5" s="43" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
       </c>
       <c r="T5" s="32" t="n"/>
       <c r="U5" s="43" t="n"/>
@@ -3843,7 +3975,7 @@
       <c r="O8" s="43" t="n"/>
       <c r="P8" s="32" t="n"/>
       <c r="Q8" s="43" t="n">
-        <v>8.100000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="R8" s="32" t="n"/>
       <c r="S8" s="43" t="n"/>
@@ -3998,36 +4130,52 @@
         </is>
       </c>
       <c r="D11" s="3" t="n"/>
-      <c r="E11" s="43" t="n">
-        <v>0.34</v>
+      <c r="E11" s="43" t="inlineStr">
+        <is>
+          <t>0.34%</t>
+        </is>
       </c>
       <c r="F11" s="34" t="n"/>
-      <c r="G11" s="43" t="n">
-        <v>0.68</v>
+      <c r="G11" s="43" t="inlineStr">
+        <is>
+          <t>0.68%</t>
+        </is>
       </c>
       <c r="H11" s="34" t="n"/>
-      <c r="I11" s="43" t="n">
-        <v>10.2</v>
+      <c r="I11" s="43" t="inlineStr">
+        <is>
+          <t>10.2%</t>
+        </is>
       </c>
       <c r="J11" s="34" t="n"/>
-      <c r="K11" s="43" t="n">
-        <v>1.46</v>
+      <c r="K11" s="43" t="inlineStr">
+        <is>
+          <t>1.46%</t>
+        </is>
       </c>
       <c r="L11" s="34" t="n"/>
-      <c r="M11" s="43" t="n">
-        <v>0.78</v>
+      <c r="M11" s="43" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
       </c>
       <c r="N11" s="34" t="n"/>
-      <c r="O11" s="43" t="n">
-        <v>0.17</v>
+      <c r="O11" s="43" t="inlineStr">
+        <is>
+          <t>0.17%</t>
+        </is>
       </c>
       <c r="P11" s="34" t="n"/>
-      <c r="Q11" s="43" t="n">
-        <v>1.15</v>
+      <c r="Q11" s="43" t="inlineStr">
+        <is>
+          <t>1.15%</t>
+        </is>
       </c>
       <c r="R11" s="34" t="n"/>
-      <c r="S11" s="43" t="n">
-        <v>0.62</v>
+      <c r="S11" s="43" t="inlineStr">
+        <is>
+          <t>0.62%</t>
+        </is>
       </c>
       <c r="T11" s="34" t="n"/>
       <c r="U11" s="43" t="n"/>
@@ -4180,36 +4328,52 @@
         </is>
       </c>
       <c r="D14" s="3" t="n"/>
-      <c r="E14" s="43" t="n">
-        <v>2.41</v>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
       </c>
       <c r="F14" s="34" t="n"/>
-      <c r="G14" s="43" t="n">
-        <v>2.46</v>
+      <c r="G14" s="43" t="inlineStr">
+        <is>
+          <t>2.46%</t>
+        </is>
       </c>
       <c r="H14" s="34" t="n"/>
-      <c r="I14" s="43" t="n">
-        <v>24.49</v>
+      <c r="I14" s="43" t="inlineStr">
+        <is>
+          <t>24.49%</t>
+        </is>
       </c>
       <c r="J14" s="34" t="n"/>
-      <c r="K14" s="43" t="n">
-        <v>0.63</v>
+      <c r="K14" s="43" t="inlineStr">
+        <is>
+          <t>0.63%</t>
+        </is>
       </c>
       <c r="L14" s="34" t="n"/>
-      <c r="M14" s="43" t="n">
-        <v>3.26</v>
+      <c r="M14" s="43" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
       </c>
       <c r="N14" s="34" t="n"/>
-      <c r="O14" s="43" t="n">
-        <v>1.76</v>
+      <c r="O14" s="43" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
       </c>
       <c r="P14" s="34" t="n"/>
-      <c r="Q14" s="43" t="n">
-        <v>2.41</v>
+      <c r="Q14" s="43" t="inlineStr">
+        <is>
+          <t>2.41%</t>
+        </is>
       </c>
       <c r="R14" s="34" t="n"/>
-      <c r="S14" s="43" t="n">
-        <v>5.08</v>
+      <c r="S14" s="43" t="inlineStr">
+        <is>
+          <t>5.08%</t>
+        </is>
       </c>
       <c r="T14" s="34" t="n"/>
       <c r="U14" s="43" t="n"/>
@@ -4362,36 +4526,52 @@
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
-      <c r="E17" s="43" t="n">
-        <v>0.78</v>
+      <c r="E17" s="43" t="inlineStr">
+        <is>
+          <t>0.78%</t>
+        </is>
       </c>
       <c r="F17" s="34" t="n"/>
-      <c r="G17" s="43" t="n">
-        <v>1.95</v>
+      <c r="G17" s="43" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
       </c>
       <c r="H17" s="34" t="n"/>
-      <c r="I17" s="43" t="n">
-        <v>12.5</v>
+      <c r="I17" s="43" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
       </c>
       <c r="J17" s="34" t="n"/>
-      <c r="K17" s="43" t="n">
-        <v>0.04</v>
+      <c r="K17" s="43" t="inlineStr">
+        <is>
+          <t>0.04%</t>
+        </is>
       </c>
       <c r="L17" s="34" t="n"/>
-      <c r="M17" s="43" t="n">
-        <v>0.46</v>
+      <c r="M17" s="43" t="inlineStr">
+        <is>
+          <t>0.46%</t>
+        </is>
       </c>
       <c r="N17" s="34" t="n"/>
-      <c r="O17" s="43" t="n">
-        <v>8.41</v>
+      <c r="O17" s="43" t="inlineStr">
+        <is>
+          <t>8.41%</t>
+        </is>
       </c>
       <c r="P17" s="34" t="n"/>
-      <c r="Q17" s="43" t="n">
-        <v>1.33</v>
+      <c r="Q17" s="43" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
       </c>
       <c r="R17" s="34" t="n"/>
-      <c r="S17" s="43" t="n">
-        <v>1.27</v>
+      <c r="S17" s="43" t="inlineStr">
+        <is>
+          <t>1.27%</t>
+        </is>
       </c>
       <c r="T17" s="34" t="n"/>
       <c r="U17" s="43" t="n"/>
@@ -4544,36 +4724,52 @@
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
-      <c r="E20" s="43" t="n">
-        <v>0.4</v>
+      <c r="E20" s="43" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
       </c>
       <c r="F20" s="34" t="n"/>
-      <c r="G20" s="43" t="n">
-        <v>0.19</v>
+      <c r="G20" s="43" t="inlineStr">
+        <is>
+          <t>0.19%</t>
+        </is>
       </c>
       <c r="H20" s="34" t="n"/>
-      <c r="I20" s="43" t="n">
-        <v>2.35</v>
+      <c r="I20" s="43" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
       </c>
       <c r="J20" s="34" t="n"/>
-      <c r="K20" s="43" t="n">
-        <v>0</v>
+      <c r="K20" s="43" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
       </c>
       <c r="L20" s="34" t="n"/>
-      <c r="M20" s="43" t="n">
-        <v>0.01</v>
+      <c r="M20" s="43" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
       </c>
       <c r="N20" s="34" t="n"/>
-      <c r="O20" s="43" t="n">
-        <v>0.01</v>
+      <c r="O20" s="43" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
       </c>
       <c r="P20" s="34" t="n"/>
-      <c r="Q20" s="43" t="n">
-        <v>0.03</v>
+      <c r="Q20" s="43" t="inlineStr">
+        <is>
+          <t>0.03%</t>
+        </is>
       </c>
       <c r="R20" s="34" t="n"/>
-      <c r="S20" s="43" t="n">
-        <v>0.61</v>
+      <c r="S20" s="43" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
       </c>
       <c r="T20" s="34" t="n"/>
       <c r="U20" s="43" t="n"/>
@@ -8672,49 +8868,49 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="43" t="inlineStr">
         <is>
-          <t>marker 1</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="43" t="inlineStr">
         <is>
-          <t>marker 2</t>
+          <t>AMY</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="43" t="inlineStr">
         <is>
-          <t>marker 3</t>
+          <t>CHOL</t>
         </is>
       </c>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="43" t="inlineStr">
         <is>
-          <t>marker 4</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="43" t="inlineStr">
         <is>
-          <t>marker 5</t>
+          <t>GLU</t>
         </is>
       </c>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="43" t="inlineStr">
         <is>
-          <t>marker 6</t>
+          <t>P-LIPA</t>
         </is>
       </c>
       <c r="P3" s="3" t="n"/>
       <c r="Q3" s="43" t="inlineStr">
         <is>
-          <t>marker 7</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="43" t="inlineStr">
         <is>
-          <t>marker 8</t>
+          <t>TRIG</t>
         </is>
       </c>
       <c r="T3" s="3" t="n"/>
@@ -8733,42 +8929,42 @@
       <c r="Z3" s="1" t="n"/>
       <c r="AA3" s="1" t="inlineStr">
         <is>
-          <t>marker 1</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>marker 2</t>
+          <t>AMY</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
         <is>
-          <t>marker 3</t>
+          <t>CHOL</t>
         </is>
       </c>
       <c r="AD3" s="1" t="inlineStr">
         <is>
-          <t>marker 4</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="AE3" s="1" t="inlineStr">
         <is>
-          <t>marker 5</t>
+          <t>GLU</t>
         </is>
       </c>
       <c r="AF3" s="1" t="inlineStr">
         <is>
-          <t>marker 6</t>
+          <t>P-LIPA</t>
         </is>
       </c>
       <c r="AG3" s="1" t="inlineStr">
         <is>
-          <t>marker 7</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AH3" s="1" t="inlineStr">
         <is>
-          <t>marker 8</t>
+          <t>TRIG</t>
         </is>
       </c>
       <c r="AI3" s="1" t="inlineStr">
@@ -8788,89 +8984,89 @@
       <c r="D4" s="29" t="n"/>
       <c r="E4" s="37" t="inlineStr">
         <is>
-          <t>marker 1(原線)</t>
+          <t>ALB(原線)</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>marker 1
+          <t>ALB
 換線後</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
         <is>
-          <t>marker 2(原線)</t>
+          <t>AMY(原線)</t>
         </is>
       </c>
       <c r="H4" s="30" t="inlineStr">
         <is>
-          <t>marker 2
+          <t>AMY
 換線後</t>
         </is>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
-          <t>marker 3(原線)</t>
+          <t>CHOL(原線)</t>
         </is>
       </c>
       <c r="J4" s="30" t="inlineStr">
         <is>
-          <t>marker 3
+          <t>CHOL
 換線後</t>
         </is>
       </c>
       <c r="K4" s="37" t="inlineStr">
         <is>
-          <t>marker 4(原線)</t>
+          <t>FRU(原線)</t>
         </is>
       </c>
       <c r="L4" s="30" t="inlineStr">
         <is>
-          <t>marker 4
+          <t>FRU
 換線後</t>
         </is>
       </c>
       <c r="M4" s="37" t="inlineStr">
         <is>
-          <t>marker 5(原線)</t>
+          <t>GLU(原線)</t>
         </is>
       </c>
       <c r="N4" s="30" t="inlineStr">
         <is>
-          <t>marker 5
+          <t>GLU
 換線後</t>
         </is>
       </c>
       <c r="O4" s="37" t="inlineStr">
         <is>
-          <t>marker 6(原線)</t>
+          <t>P-LIPA(原線)</t>
         </is>
       </c>
       <c r="P4" s="30" t="inlineStr">
         <is>
-          <t>marker 6
+          <t>P-LIPA
 換線後</t>
         </is>
       </c>
       <c r="Q4" s="37" t="inlineStr">
         <is>
-          <t>marker 7(原線)</t>
+          <t>TP(原線)</t>
         </is>
       </c>
       <c r="R4" s="30" t="inlineStr">
         <is>
-          <t>marker 7
+          <t>TP
 換線後</t>
         </is>
       </c>
       <c r="S4" s="37" t="inlineStr">
         <is>
-          <t>marker 8(原線)</t>
+          <t>TRIG(原線)</t>
         </is>
       </c>
       <c r="T4" s="30" t="inlineStr">
         <is>
-          <t>marker 8
+          <t>TRIG
 換線後</t>
         </is>
       </c>
@@ -10016,35 +10212,99 @@
         </is>
       </c>
       <c r="D34" s="1" t="n"/>
-      <c r="E34" s="43" t="n"/>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="43" t="n"/>
+      <c r="G34" s="43" t="inlineStr">
+        <is>
+          <t>AMY</t>
+        </is>
+      </c>
       <c r="H34" s="3" t="n"/>
-      <c r="I34" s="43" t="n"/>
+      <c r="I34" s="43" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="n"/>
-      <c r="K34" s="43" t="n"/>
+      <c r="K34" s="43" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
       <c r="L34" s="3" t="n"/>
-      <c r="M34" s="43" t="n"/>
+      <c r="M34" s="43" t="inlineStr">
+        <is>
+          <t>GLU</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="n"/>
-      <c r="O34" s="43" t="n"/>
+      <c r="O34" s="43" t="inlineStr">
+        <is>
+          <t>P-LIPA</t>
+        </is>
+      </c>
       <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="43" t="n"/>
+      <c r="Q34" s="43" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
       <c r="R34" s="3" t="n"/>
-      <c r="S34" s="43" t="n"/>
+      <c r="S34" s="43" t="inlineStr">
+        <is>
+          <t>TRIG</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="n"/>
       <c r="U34" s="43" t="n"/>
       <c r="V34" s="3" t="n"/>
       <c r="W34" s="43" t="n"/>
       <c r="X34" s="3" t="n"/>
       <c r="Z34" s="1" t="n"/>
-      <c r="AA34" s="1" t="n"/>
-      <c r="AB34" s="1" t="n"/>
-      <c r="AC34" s="1" t="n"/>
-      <c r="AD34" s="1" t="n"/>
-      <c r="AE34" s="1" t="n"/>
-      <c r="AF34" s="1" t="n"/>
-      <c r="AG34" s="1" t="n"/>
-      <c r="AH34" s="1" t="n"/>
+      <c r="AA34" s="1" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="AB34" s="1" t="inlineStr">
+        <is>
+          <t>AMY</t>
+        </is>
+      </c>
+      <c r="AC34" s="1" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
+      <c r="AD34" s="1" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
+      <c r="AE34" s="1" t="inlineStr">
+        <is>
+          <t>GLU</t>
+        </is>
+      </c>
+      <c r="AF34" s="1" t="inlineStr">
+        <is>
+          <t>P-LIPA</t>
+        </is>
+      </c>
+      <c r="AG34" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="AH34" s="1" t="inlineStr">
+        <is>
+          <t>TRIG</t>
+        </is>
+      </c>
       <c r="AI34" s="1" t="n"/>
       <c r="AJ34" s="1" t="n"/>
       <c r="AK34" s="13" t="inlineStr">
@@ -10056,22 +10316,94 @@
     <row r="35" ht="33" customHeight="1">
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="1" t="n"/>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="30" t="n"/>
-      <c r="I35" s="37" t="n"/>
-      <c r="J35" s="30" t="n"/>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="30" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="30" t="n"/>
-      <c r="O35" s="37" t="n"/>
-      <c r="P35" s="30" t="n"/>
-      <c r="Q35" s="37" t="n"/>
-      <c r="R35" s="30" t="n"/>
-      <c r="S35" s="37" t="n"/>
-      <c r="T35" s="30" t="n"/>
+      <c r="E35" s="37" t="inlineStr">
+        <is>
+          <t>ALB(原線)</t>
+        </is>
+      </c>
+      <c r="F35" s="30" t="inlineStr">
+        <is>
+          <t>ALB
+換線後</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="inlineStr">
+        <is>
+          <t>AMY(原線)</t>
+        </is>
+      </c>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>AMY
+換線後</t>
+        </is>
+      </c>
+      <c r="I35" s="37" t="inlineStr">
+        <is>
+          <t>CHOL(原線)</t>
+        </is>
+      </c>
+      <c r="J35" s="30" t="inlineStr">
+        <is>
+          <t>CHOL
+換線後</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="inlineStr">
+        <is>
+          <t>FRU(原線)</t>
+        </is>
+      </c>
+      <c r="L35" s="30" t="inlineStr">
+        <is>
+          <t>FRU
+換線後</t>
+        </is>
+      </c>
+      <c r="M35" s="37" t="inlineStr">
+        <is>
+          <t>GLU(原線)</t>
+        </is>
+      </c>
+      <c r="N35" s="30" t="inlineStr">
+        <is>
+          <t>GLU
+換線後</t>
+        </is>
+      </c>
+      <c r="O35" s="37" t="inlineStr">
+        <is>
+          <t>P-LIPA(原線)</t>
+        </is>
+      </c>
+      <c r="P35" s="30" t="inlineStr">
+        <is>
+          <t>P-LIPA
+換線後</t>
+        </is>
+      </c>
+      <c r="Q35" s="37" t="inlineStr">
+        <is>
+          <t>TP(原線)</t>
+        </is>
+      </c>
+      <c r="R35" s="30" t="inlineStr">
+        <is>
+          <t>TP
+換線後</t>
+        </is>
+      </c>
+      <c r="S35" s="37" t="inlineStr">
+        <is>
+          <t>TRIG(原線)</t>
+        </is>
+      </c>
+      <c r="T35" s="30" t="inlineStr">
+        <is>
+          <t>TRIG
+換線後</t>
+        </is>
+      </c>
       <c r="U35" s="37" t="n"/>
       <c r="V35" s="30" t="n"/>
       <c r="W35" s="37" t="n"/>
@@ -10090,16 +10422,7 @@
       <c r="AK35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C36" s="1" t="n"/>
       <c r="D36" s="1" t="n"/>
       <c r="E36" s="43" t="n"/>
       <c r="F36" s="34" t="n"/>
@@ -10135,16 +10458,7 @@
       <c r="AK36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C37" s="1" t="n"/>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="43" t="n"/>
       <c r="F37" s="34" t="n"/>
@@ -10180,16 +10494,7 @@
       <c r="AK37" s="1" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C38" s="1" t="n"/>
       <c r="D38" s="1" t="n"/>
       <c r="E38" s="43" t="n"/>
       <c r="F38" s="34" t="n"/>
@@ -10225,16 +10530,7 @@
       <c r="AK38" s="1" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C39" s="1" t="n"/>
       <c r="D39" s="1" t="n"/>
       <c r="E39" s="43" t="n"/>
       <c r="F39" s="34" t="n"/>
@@ -10270,16 +10566,7 @@
       <c r="AK39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C40" s="1" t="n"/>
       <c r="D40" s="1" t="n"/>
       <c r="E40" s="43" t="n"/>
       <c r="F40" s="34" t="n"/>
@@ -10315,16 +10602,7 @@
       <c r="AK40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C41" s="1" t="n"/>
       <c r="D41" s="1" t="n"/>
       <c r="E41" s="43" t="n"/>
       <c r="F41" s="34" t="n"/>
@@ -10360,16 +10638,7 @@
       <c r="AK41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C42" s="1" t="n"/>
       <c r="D42" s="1" t="n"/>
       <c r="E42" s="43" t="n"/>
       <c r="F42" s="34" t="n"/>
@@ -10405,16 +10674,7 @@
       <c r="AK42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C43" s="1" t="n"/>
       <c r="D43" s="1" t="n"/>
       <c r="E43" s="43" t="n"/>
       <c r="F43" s="34" t="n"/>
@@ -10450,16 +10710,7 @@
       <c r="AK43" s="1" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C44" s="1" t="n"/>
       <c r="D44" s="1" t="n"/>
       <c r="E44" s="43" t="n"/>
       <c r="F44" s="34" t="n"/>
@@ -10495,16 +10746,7 @@
       <c r="AK44" s="1" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Canine 1</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C45" s="1" t="n"/>
       <c r="D45" s="1" t="n"/>
       <c r="E45" s="43" t="n"/>
       <c r="F45" s="34" t="n"/>
@@ -10540,16 +10782,8 @@
       <c r="AK45" s="1" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="8" t="n"/>
       <c r="D46" s="1" t="n"/>
       <c r="E46" s="43" t="n"/>
       <c r="F46" s="34" t="n"/>
@@ -10585,16 +10819,8 @@
       <c r="AK46" s="1" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="8" t="n"/>
       <c r="D47" s="1" t="n"/>
       <c r="E47" s="43" t="n"/>
       <c r="F47" s="34" t="n"/>
@@ -10630,16 +10856,8 @@
       <c r="AK47" s="1" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="8" t="n"/>
       <c r="D48" s="1" t="n"/>
       <c r="E48" s="43" t="n"/>
       <c r="F48" s="34" t="n"/>
@@ -10675,16 +10893,8 @@
       <c r="AK48" s="1" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="8" t="n"/>
       <c r="D49" s="1" t="n"/>
       <c r="E49" s="43" t="n"/>
       <c r="F49" s="34" t="n"/>
@@ -10720,16 +10930,8 @@
       <c r="AK49" s="1" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="8" t="n"/>
       <c r="D50" s="1" t="n"/>
       <c r="E50" s="43" t="n"/>
       <c r="F50" s="34" t="n"/>
@@ -10765,16 +10967,8 @@
       <c r="AK50" s="1" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="8" t="n"/>
       <c r="D51" s="1" t="n"/>
       <c r="E51" s="43" t="n"/>
       <c r="F51" s="34" t="n"/>
@@ -10810,16 +11004,8 @@
       <c r="AK51" s="1" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="8" t="n"/>
       <c r="D52" s="1" t="n"/>
       <c r="E52" s="43" t="n"/>
       <c r="F52" s="34" t="n"/>
@@ -10855,16 +11041,8 @@
       <c r="AK52" s="1" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="8" t="n"/>
       <c r="D53" s="1" t="n"/>
       <c r="E53" s="43" t="n"/>
       <c r="F53" s="34" t="n"/>
@@ -10900,16 +11078,8 @@
       <c r="AK53" s="1" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="8" t="n"/>
       <c r="D54" s="1" t="n"/>
       <c r="E54" s="43" t="n"/>
       <c r="F54" s="34" t="n"/>
@@ -10945,16 +11115,8 @@
       <c r="AK54" s="1" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Canine 2</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="8" t="n"/>
       <c r="D55" s="1" t="n"/>
       <c r="E55" s="43" t="n"/>
       <c r="F55" s="34" t="n"/>
@@ -10990,16 +11152,7 @@
       <c r="AK55" s="1" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C56" s="1" t="n"/>
       <c r="D56" s="1" t="n"/>
       <c r="E56" s="43" t="n"/>
       <c r="F56" s="34" t="n"/>
@@ -11035,16 +11188,7 @@
       <c r="AK56" s="1" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C57" s="1" t="n"/>
       <c r="D57" s="1" t="n"/>
       <c r="E57" s="43" t="n"/>
       <c r="F57" s="34" t="n"/>
@@ -11080,16 +11224,7 @@
       <c r="AK57" s="1" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C58" s="1" t="n"/>
       <c r="D58" s="1" t="n"/>
       <c r="E58" s="43" t="n"/>
       <c r="F58" s="34" t="n"/>
@@ -11125,16 +11260,7 @@
       <c r="AK58" s="1" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C59" s="1" t="n"/>
       <c r="D59" s="1" t="n"/>
       <c r="E59" s="43" t="n"/>
       <c r="F59" s="34" t="n"/>
@@ -11170,16 +11296,7 @@
       <c r="AK59" s="1" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C60" s="1" t="n"/>
       <c r="D60" s="1" t="n"/>
       <c r="E60" s="43" t="n"/>
       <c r="F60" s="34" t="n"/>
@@ -11215,16 +11332,7 @@
       <c r="AK60" s="1" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C61" s="1" t="n"/>
       <c r="D61" s="1" t="n"/>
       <c r="E61" s="43" t="n"/>
       <c r="F61" s="34" t="n"/>
@@ -11260,16 +11368,7 @@
       <c r="AK61" s="1" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C62" s="1" t="n"/>
       <c r="D62" s="1" t="n"/>
       <c r="E62" s="43" t="n"/>
       <c r="F62" s="34" t="n"/>
@@ -11305,16 +11404,7 @@
       <c r="AK62" s="1" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C63" s="1" t="n"/>
       <c r="D63" s="1" t="n"/>
       <c r="E63" s="43" t="n"/>
       <c r="F63" s="34" t="n"/>
@@ -11350,16 +11440,7 @@
       <c r="AK63" s="1" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C64" s="1" t="n"/>
       <c r="D64" s="1" t="n"/>
       <c r="E64" s="43" t="n"/>
       <c r="F64" s="34" t="n"/>
@@ -11395,16 +11476,7 @@
       <c r="AK64" s="1" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Canine 3</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C65" s="1" t="n"/>
       <c r="D65" s="1" t="n"/>
       <c r="E65" s="43" t="n"/>
       <c r="F65" s="34" t="n"/>
@@ -11440,16 +11512,8 @@
       <c r="AK65" s="1" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="8" t="n"/>
       <c r="D66" s="1" t="n"/>
       <c r="E66" s="43" t="n"/>
       <c r="F66" s="34" t="n"/>
@@ -11485,16 +11549,8 @@
       <c r="AK66" s="1" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="8" t="n"/>
       <c r="D67" s="1" t="n"/>
       <c r="E67" s="43" t="n"/>
       <c r="F67" s="34" t="n"/>
@@ -11530,16 +11586,8 @@
       <c r="AK67" s="1" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="8" t="n"/>
       <c r="D68" s="1" t="n"/>
       <c r="E68" s="43" t="n"/>
       <c r="F68" s="34" t="n"/>
@@ -11575,16 +11623,8 @@
       <c r="AK68" s="1" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="8" t="n"/>
       <c r="D69" s="1" t="n"/>
       <c r="E69" s="43" t="n"/>
       <c r="F69" s="34" t="n"/>
@@ -11620,16 +11660,8 @@
       <c r="AK69" s="1" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="8" t="n"/>
       <c r="D70" s="1" t="n"/>
       <c r="E70" s="43" t="n"/>
       <c r="F70" s="34" t="n"/>
@@ -11665,16 +11697,8 @@
       <c r="AK70" s="1" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="8" t="n"/>
       <c r="D71" s="1" t="n"/>
       <c r="E71" s="43" t="n"/>
       <c r="F71" s="34" t="n"/>
@@ -11710,16 +11734,8 @@
       <c r="AK71" s="1" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="8" t="n"/>
       <c r="D72" s="1" t="n"/>
       <c r="E72" s="43" t="n"/>
       <c r="F72" s="34" t="n"/>
@@ -11755,16 +11771,8 @@
       <c r="AK72" s="1" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="8" t="n"/>
       <c r="D73" s="1" t="n"/>
       <c r="E73" s="43" t="n"/>
       <c r="F73" s="34" t="n"/>
@@ -11800,16 +11808,8 @@
       <c r="AK73" s="1" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="8" t="n"/>
       <c r="D74" s="1" t="n"/>
       <c r="E74" s="43" t="n"/>
       <c r="F74" s="34" t="n"/>
@@ -11845,16 +11845,8 @@
       <c r="AK74" s="1" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Canine 4</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="8" t="n"/>
       <c r="D75" s="1" t="n"/>
       <c r="E75" s="43" t="n"/>
       <c r="F75" s="34" t="n"/>
@@ -11890,16 +11882,7 @@
       <c r="AK75" s="1" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C76" s="1" t="n"/>
       <c r="D76" s="1" t="n"/>
       <c r="E76" s="43" t="n"/>
       <c r="F76" s="34" t="n"/>
@@ -11935,16 +11918,7 @@
       <c r="AK76" s="1" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C77" s="1" t="n"/>
       <c r="D77" s="1" t="n"/>
       <c r="E77" s="43" t="n"/>
       <c r="F77" s="34" t="n"/>
@@ -11980,16 +11954,7 @@
       <c r="AK77" s="1" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C78" s="1" t="n"/>
       <c r="D78" s="1" t="n"/>
       <c r="E78" s="43" t="n"/>
       <c r="F78" s="34" t="n"/>
@@ -12025,16 +11990,7 @@
       <c r="AK78" s="1" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C79" s="1" t="n"/>
       <c r="D79" s="1" t="n"/>
       <c r="E79" s="43" t="n"/>
       <c r="F79" s="34" t="n"/>
@@ -12070,16 +12026,7 @@
       <c r="AK79" s="1" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C80" s="1" t="n"/>
       <c r="D80" s="1" t="n"/>
       <c r="E80" s="43" t="n"/>
       <c r="F80" s="34" t="n"/>
@@ -12115,16 +12062,7 @@
       <c r="AK80" s="1" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C81" s="1" t="n"/>
       <c r="D81" s="1" t="n"/>
       <c r="E81" s="43" t="n"/>
       <c r="F81" s="34" t="n"/>
@@ -12160,16 +12098,7 @@
       <c r="AK81" s="1" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C82" s="1" t="n"/>
       <c r="D82" s="1" t="n"/>
       <c r="E82" s="43" t="n"/>
       <c r="F82" s="34" t="n"/>
@@ -12205,16 +12134,7 @@
       <c r="AK82" s="1" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C83" s="1" t="n"/>
       <c r="D83" s="1" t="n"/>
       <c r="E83" s="43" t="n"/>
       <c r="F83" s="34" t="n"/>
@@ -12250,16 +12170,7 @@
       <c r="AK83" s="1" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C84" s="1" t="n"/>
       <c r="D84" s="1" t="n"/>
       <c r="E84" s="43" t="n"/>
       <c r="F84" s="34" t="n"/>
@@ -12295,16 +12206,7 @@
       <c r="AK84" s="1" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Canine 5</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C85" s="1" t="n"/>
       <c r="D85" s="1" t="n"/>
       <c r="E85" s="43" t="n"/>
       <c r="F85" s="34" t="n"/>
@@ -12340,16 +12242,8 @@
       <c r="AK85" s="1" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="8" t="n"/>
       <c r="D86" s="1" t="n"/>
       <c r="E86" s="43" t="n"/>
       <c r="F86" s="34" t="n"/>
@@ -12385,16 +12279,8 @@
       <c r="AK86" s="1" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="8" t="n"/>
       <c r="D87" s="1" t="n"/>
       <c r="E87" s="43" t="n"/>
       <c r="F87" s="34" t="n"/>
@@ -12430,16 +12316,8 @@
       <c r="AK87" s="1" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="8" t="n"/>
       <c r="D88" s="1" t="n"/>
       <c r="E88" s="43" t="n"/>
       <c r="F88" s="34" t="n"/>
@@ -12475,16 +12353,8 @@
       <c r="AK88" s="1" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="8" t="n"/>
       <c r="D89" s="1" t="n"/>
       <c r="E89" s="43" t="n"/>
       <c r="F89" s="34" t="n"/>
@@ -12520,16 +12390,8 @@
       <c r="AK89" s="1" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="8" t="n"/>
       <c r="D90" s="1" t="n"/>
       <c r="E90" s="43" t="n"/>
       <c r="F90" s="34" t="n"/>
@@ -12565,16 +12427,8 @@
       <c r="AK90" s="1" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="8" t="n"/>
       <c r="D91" s="1" t="n"/>
       <c r="E91" s="43" t="n"/>
       <c r="F91" s="34" t="n"/>
@@ -12610,16 +12464,8 @@
       <c r="AK91" s="1" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="8" t="n"/>
       <c r="D92" s="1" t="n"/>
       <c r="E92" s="43" t="n"/>
       <c r="F92" s="34" t="n"/>
@@ -12655,16 +12501,8 @@
       <c r="AK92" s="1" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="8" t="n"/>
       <c r="D93" s="1" t="n"/>
       <c r="E93" s="43" t="n"/>
       <c r="F93" s="34" t="n"/>
@@ -12700,16 +12538,8 @@
       <c r="AK93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="8" t="n"/>
       <c r="D94" s="1" t="n"/>
       <c r="E94" s="43" t="n"/>
       <c r="F94" s="34" t="n"/>
@@ -12745,16 +12575,8 @@
       <c r="AK94" s="1" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Canine 6</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="8" t="n"/>
       <c r="D95" s="1" t="n"/>
       <c r="E95" s="43" t="n"/>
       <c r="F95" s="34" t="n"/>
@@ -14039,49 +13861,49 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="43" t="inlineStr">
         <is>
-          <t>marker 1</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="43" t="inlineStr">
         <is>
-          <t>marker 2</t>
+          <t>AMY</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="43" t="inlineStr">
         <is>
-          <t>marker 3</t>
+          <t>CHOL</t>
         </is>
       </c>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="43" t="inlineStr">
         <is>
-          <t>marker 4</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="43" t="inlineStr">
         <is>
-          <t>marker 5</t>
+          <t>GLU</t>
         </is>
       </c>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="43" t="inlineStr">
         <is>
-          <t>marker 6</t>
+          <t>P-LIPA</t>
         </is>
       </c>
       <c r="P3" s="3" t="n"/>
       <c r="Q3" s="43" t="inlineStr">
         <is>
-          <t>marker 7</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="43" t="inlineStr">
         <is>
-          <t>marker 8</t>
+          <t>TRIG</t>
         </is>
       </c>
       <c r="T3" s="3" t="n"/>
@@ -14100,42 +13922,42 @@
       <c r="Z3" s="1" t="n"/>
       <c r="AA3" s="1" t="inlineStr">
         <is>
-          <t>marker 1</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>marker 2</t>
+          <t>AMY</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
         <is>
-          <t>marker 3</t>
+          <t>CHOL</t>
         </is>
       </c>
       <c r="AD3" s="1" t="inlineStr">
         <is>
-          <t>marker 4</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="AE3" s="1" t="inlineStr">
         <is>
-          <t>marker 5</t>
+          <t>GLU</t>
         </is>
       </c>
       <c r="AF3" s="1" t="inlineStr">
         <is>
-          <t>marker 6</t>
+          <t>P-LIPA</t>
         </is>
       </c>
       <c r="AG3" s="1" t="inlineStr">
         <is>
-          <t>marker 7</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AH3" s="1" t="inlineStr">
         <is>
-          <t>marker 8</t>
+          <t>TRIG</t>
         </is>
       </c>
       <c r="AI3" s="1" t="inlineStr">
@@ -14155,89 +13977,89 @@
       <c r="D4" s="29" t="n"/>
       <c r="E4" s="37" t="inlineStr">
         <is>
-          <t>marker 1(原線)</t>
+          <t>ALB(原線)</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>marker 1
+          <t>ALB
 換線後</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
         <is>
-          <t>marker 2(原線)</t>
+          <t>AMY(原線)</t>
         </is>
       </c>
       <c r="H4" s="30" t="inlineStr">
         <is>
-          <t>marker 2
+          <t>AMY
 換線後</t>
         </is>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
-          <t>marker 3(原線)</t>
+          <t>CHOL(原線)</t>
         </is>
       </c>
       <c r="J4" s="30" t="inlineStr">
         <is>
-          <t>marker 3
+          <t>CHOL
 換線後</t>
         </is>
       </c>
       <c r="K4" s="37" t="inlineStr">
         <is>
-          <t>marker 4(原線)</t>
+          <t>FRU(原線)</t>
         </is>
       </c>
       <c r="L4" s="30" t="inlineStr">
         <is>
-          <t>marker 4
+          <t>FRU
 換線後</t>
         </is>
       </c>
       <c r="M4" s="37" t="inlineStr">
         <is>
-          <t>marker 5(原線)</t>
+          <t>GLU(原線)</t>
         </is>
       </c>
       <c r="N4" s="30" t="inlineStr">
         <is>
-          <t>marker 5
+          <t>GLU
 換線後</t>
         </is>
       </c>
       <c r="O4" s="37" t="inlineStr">
         <is>
-          <t>marker 6(原線)</t>
+          <t>P-LIPA(原線)</t>
         </is>
       </c>
       <c r="P4" s="30" t="inlineStr">
         <is>
-          <t>marker 6
+          <t>P-LIPA
 換線後</t>
         </is>
       </c>
       <c r="Q4" s="37" t="inlineStr">
         <is>
-          <t>marker 7(原線)</t>
+          <t>TP(原線)</t>
         </is>
       </c>
       <c r="R4" s="30" t="inlineStr">
         <is>
-          <t>marker 7
+          <t>TP
 換線後</t>
         </is>
       </c>
       <c r="S4" s="37" t="inlineStr">
         <is>
-          <t>marker 8(原線)</t>
+          <t>TRIG(原線)</t>
         </is>
       </c>
       <c r="T4" s="30" t="inlineStr">
         <is>
-          <t>marker 8
+          <t>TRIG
 換線後</t>
         </is>
       </c>
@@ -15383,35 +15205,99 @@
         </is>
       </c>
       <c r="D34" s="1" t="n"/>
-      <c r="E34" s="43" t="n"/>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="43" t="n"/>
+      <c r="G34" s="43" t="inlineStr">
+        <is>
+          <t>AMY</t>
+        </is>
+      </c>
       <c r="H34" s="3" t="n"/>
-      <c r="I34" s="43" t="n"/>
+      <c r="I34" s="43" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="n"/>
-      <c r="K34" s="43" t="n"/>
+      <c r="K34" s="43" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
       <c r="L34" s="3" t="n"/>
-      <c r="M34" s="43" t="n"/>
+      <c r="M34" s="43" t="inlineStr">
+        <is>
+          <t>GLU</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="n"/>
-      <c r="O34" s="43" t="n"/>
+      <c r="O34" s="43" t="inlineStr">
+        <is>
+          <t>P-LIPA</t>
+        </is>
+      </c>
       <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="43" t="n"/>
+      <c r="Q34" s="43" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
       <c r="R34" s="3" t="n"/>
-      <c r="S34" s="43" t="n"/>
+      <c r="S34" s="43" t="inlineStr">
+        <is>
+          <t>TRIG</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="n"/>
       <c r="U34" s="43" t="n"/>
       <c r="V34" s="3" t="n"/>
       <c r="W34" s="43" t="n"/>
       <c r="X34" s="3" t="n"/>
       <c r="Z34" s="1" t="n"/>
-      <c r="AA34" s="1" t="n"/>
-      <c r="AB34" s="1" t="n"/>
-      <c r="AC34" s="1" t="n"/>
-      <c r="AD34" s="1" t="n"/>
-      <c r="AE34" s="1" t="n"/>
-      <c r="AF34" s="1" t="n"/>
-      <c r="AG34" s="1" t="n"/>
-      <c r="AH34" s="1" t="n"/>
+      <c r="AA34" s="1" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="AB34" s="1" t="inlineStr">
+        <is>
+          <t>AMY</t>
+        </is>
+      </c>
+      <c r="AC34" s="1" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
+      <c r="AD34" s="1" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
+      <c r="AE34" s="1" t="inlineStr">
+        <is>
+          <t>GLU</t>
+        </is>
+      </c>
+      <c r="AF34" s="1" t="inlineStr">
+        <is>
+          <t>P-LIPA</t>
+        </is>
+      </c>
+      <c r="AG34" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="AH34" s="1" t="inlineStr">
+        <is>
+          <t>TRIG</t>
+        </is>
+      </c>
       <c r="AI34" s="1" t="n"/>
       <c r="AJ34" s="1" t="n"/>
       <c r="AK34" s="13" t="inlineStr">
@@ -15423,22 +15309,94 @@
     <row r="35" ht="33" customHeight="1">
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="1" t="n"/>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="30" t="n"/>
-      <c r="I35" s="37" t="n"/>
-      <c r="J35" s="30" t="n"/>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="30" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="30" t="n"/>
-      <c r="O35" s="37" t="n"/>
-      <c r="P35" s="30" t="n"/>
-      <c r="Q35" s="37" t="n"/>
-      <c r="R35" s="30" t="n"/>
-      <c r="S35" s="37" t="n"/>
-      <c r="T35" s="30" t="n"/>
+      <c r="E35" s="37" t="inlineStr">
+        <is>
+          <t>ALB(原線)</t>
+        </is>
+      </c>
+      <c r="F35" s="30" t="inlineStr">
+        <is>
+          <t>ALB
+換線後</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="inlineStr">
+        <is>
+          <t>AMY(原線)</t>
+        </is>
+      </c>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>AMY
+換線後</t>
+        </is>
+      </c>
+      <c r="I35" s="37" t="inlineStr">
+        <is>
+          <t>CHOL(原線)</t>
+        </is>
+      </c>
+      <c r="J35" s="30" t="inlineStr">
+        <is>
+          <t>CHOL
+換線後</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="inlineStr">
+        <is>
+          <t>FRU(原線)</t>
+        </is>
+      </c>
+      <c r="L35" s="30" t="inlineStr">
+        <is>
+          <t>FRU
+換線後</t>
+        </is>
+      </c>
+      <c r="M35" s="37" t="inlineStr">
+        <is>
+          <t>GLU(原線)</t>
+        </is>
+      </c>
+      <c r="N35" s="30" t="inlineStr">
+        <is>
+          <t>GLU
+換線後</t>
+        </is>
+      </c>
+      <c r="O35" s="37" t="inlineStr">
+        <is>
+          <t>P-LIPA(原線)</t>
+        </is>
+      </c>
+      <c r="P35" s="30" t="inlineStr">
+        <is>
+          <t>P-LIPA
+換線後</t>
+        </is>
+      </c>
+      <c r="Q35" s="37" t="inlineStr">
+        <is>
+          <t>TP(原線)</t>
+        </is>
+      </c>
+      <c r="R35" s="30" t="inlineStr">
+        <is>
+          <t>TP
+換線後</t>
+        </is>
+      </c>
+      <c r="S35" s="37" t="inlineStr">
+        <is>
+          <t>TRIG(原線)</t>
+        </is>
+      </c>
+      <c r="T35" s="30" t="inlineStr">
+        <is>
+          <t>TRIG
+換線後</t>
+        </is>
+      </c>
       <c r="U35" s="37" t="n"/>
       <c r="V35" s="30" t="n"/>
       <c r="W35" s="37" t="n"/>
@@ -15457,16 +15415,7 @@
       <c r="AK35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C36" s="1" t="n"/>
       <c r="D36" s="1" t="n"/>
       <c r="E36" s="43" t="n"/>
       <c r="F36" s="34" t="n"/>
@@ -15502,16 +15451,7 @@
       <c r="AK36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C37" s="1" t="n"/>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="43" t="n"/>
       <c r="F37" s="34" t="n"/>
@@ -15547,16 +15487,7 @@
       <c r="AK37" s="1" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C38" s="1" t="n"/>
       <c r="D38" s="1" t="n"/>
       <c r="E38" s="43" t="n"/>
       <c r="F38" s="34" t="n"/>
@@ -15592,16 +15523,7 @@
       <c r="AK38" s="1" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C39" s="1" t="n"/>
       <c r="D39" s="1" t="n"/>
       <c r="E39" s="43" t="n"/>
       <c r="F39" s="34" t="n"/>
@@ -15637,16 +15559,7 @@
       <c r="AK39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C40" s="1" t="n"/>
       <c r="D40" s="1" t="n"/>
       <c r="E40" s="43" t="n"/>
       <c r="F40" s="34" t="n"/>
@@ -15682,16 +15595,7 @@
       <c r="AK40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C41" s="1" t="n"/>
       <c r="D41" s="1" t="n"/>
       <c r="E41" s="43" t="n"/>
       <c r="F41" s="34" t="n"/>
@@ -15727,16 +15631,7 @@
       <c r="AK41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C42" s="1" t="n"/>
       <c r="D42" s="1" t="n"/>
       <c r="E42" s="43" t="n"/>
       <c r="F42" s="34" t="n"/>
@@ -15772,16 +15667,7 @@
       <c r="AK42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C43" s="1" t="n"/>
       <c r="D43" s="1" t="n"/>
       <c r="E43" s="43" t="n"/>
       <c r="F43" s="34" t="n"/>
@@ -15817,16 +15703,7 @@
       <c r="AK43" s="1" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C44" s="1" t="n"/>
       <c r="D44" s="1" t="n"/>
       <c r="E44" s="43" t="n"/>
       <c r="F44" s="34" t="n"/>
@@ -15862,16 +15739,7 @@
       <c r="AK44" s="1" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Feline 1</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C45" s="1" t="n"/>
       <c r="D45" s="1" t="n"/>
       <c r="E45" s="43" t="n"/>
       <c r="F45" s="34" t="n"/>
@@ -15907,16 +15775,8 @@
       <c r="AK45" s="1" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="8" t="n"/>
       <c r="D46" s="1" t="n"/>
       <c r="E46" s="43" t="n"/>
       <c r="F46" s="34" t="n"/>
@@ -15952,16 +15812,8 @@
       <c r="AK46" s="1" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="8" t="n"/>
       <c r="D47" s="1" t="n"/>
       <c r="E47" s="43" t="n"/>
       <c r="F47" s="34" t="n"/>
@@ -15997,16 +15849,8 @@
       <c r="AK47" s="1" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="8" t="n"/>
       <c r="D48" s="1" t="n"/>
       <c r="E48" s="43" t="n"/>
       <c r="F48" s="34" t="n"/>
@@ -16042,16 +15886,8 @@
       <c r="AK48" s="1" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="8" t="n"/>
       <c r="D49" s="1" t="n"/>
       <c r="E49" s="43" t="n"/>
       <c r="F49" s="34" t="n"/>
@@ -16087,16 +15923,8 @@
       <c r="AK49" s="1" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="8" t="n"/>
       <c r="D50" s="1" t="n"/>
       <c r="E50" s="43" t="n"/>
       <c r="F50" s="34" t="n"/>
@@ -16132,16 +15960,8 @@
       <c r="AK50" s="1" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="8" t="n"/>
       <c r="D51" s="1" t="n"/>
       <c r="E51" s="43" t="n"/>
       <c r="F51" s="34" t="n"/>
@@ -16177,16 +15997,8 @@
       <c r="AK51" s="1" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="8" t="n"/>
       <c r="D52" s="1" t="n"/>
       <c r="E52" s="43" t="n"/>
       <c r="F52" s="34" t="n"/>
@@ -16222,16 +16034,8 @@
       <c r="AK52" s="1" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="8" t="n"/>
       <c r="D53" s="1" t="n"/>
       <c r="E53" s="43" t="n"/>
       <c r="F53" s="34" t="n"/>
@@ -16267,16 +16071,8 @@
       <c r="AK53" s="1" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="8" t="n"/>
       <c r="D54" s="1" t="n"/>
       <c r="E54" s="43" t="n"/>
       <c r="F54" s="34" t="n"/>
@@ -16312,16 +16108,8 @@
       <c r="AK54" s="1" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Feline 2</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="8" t="n"/>
       <c r="D55" s="1" t="n"/>
       <c r="E55" s="43" t="n"/>
       <c r="F55" s="34" t="n"/>
@@ -16357,16 +16145,7 @@
       <c r="AK55" s="1" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C56" s="1" t="n"/>
       <c r="D56" s="1" t="n"/>
       <c r="E56" s="43" t="n"/>
       <c r="F56" s="34" t="n"/>
@@ -16402,16 +16181,7 @@
       <c r="AK56" s="1" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C57" s="1" t="n"/>
       <c r="D57" s="1" t="n"/>
       <c r="E57" s="43" t="n"/>
       <c r="F57" s="34" t="n"/>
@@ -16447,16 +16217,7 @@
       <c r="AK57" s="1" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C58" s="1" t="n"/>
       <c r="D58" s="1" t="n"/>
       <c r="E58" s="43" t="n"/>
       <c r="F58" s="34" t="n"/>
@@ -16492,16 +16253,7 @@
       <c r="AK58" s="1" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C59" s="1" t="n"/>
       <c r="D59" s="1" t="n"/>
       <c r="E59" s="43" t="n"/>
       <c r="F59" s="34" t="n"/>
@@ -16537,16 +16289,7 @@
       <c r="AK59" s="1" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C60" s="1" t="n"/>
       <c r="D60" s="1" t="n"/>
       <c r="E60" s="43" t="n"/>
       <c r="F60" s="34" t="n"/>
@@ -16582,16 +16325,7 @@
       <c r="AK60" s="1" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C61" s="1" t="n"/>
       <c r="D61" s="1" t="n"/>
       <c r="E61" s="43" t="n"/>
       <c r="F61" s="34" t="n"/>
@@ -16627,16 +16361,7 @@
       <c r="AK61" s="1" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C62" s="1" t="n"/>
       <c r="D62" s="1" t="n"/>
       <c r="E62" s="43" t="n"/>
       <c r="F62" s="34" t="n"/>
@@ -16672,16 +16397,7 @@
       <c r="AK62" s="1" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C63" s="1" t="n"/>
       <c r="D63" s="1" t="n"/>
       <c r="E63" s="43" t="n"/>
       <c r="F63" s="34" t="n"/>
@@ -16717,16 +16433,7 @@
       <c r="AK63" s="1" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C64" s="1" t="n"/>
       <c r="D64" s="1" t="n"/>
       <c r="E64" s="43" t="n"/>
       <c r="F64" s="34" t="n"/>
@@ -16762,16 +16469,7 @@
       <c r="AK64" s="1" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Feline 3</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C65" s="1" t="n"/>
       <c r="D65" s="1" t="n"/>
       <c r="E65" s="43" t="n"/>
       <c r="F65" s="34" t="n"/>
@@ -16807,16 +16505,8 @@
       <c r="AK65" s="1" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="8" t="n"/>
       <c r="D66" s="1" t="n"/>
       <c r="E66" s="43" t="n"/>
       <c r="F66" s="34" t="n"/>
@@ -16852,16 +16542,8 @@
       <c r="AK66" s="1" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="8" t="n"/>
       <c r="D67" s="1" t="n"/>
       <c r="E67" s="43" t="n"/>
       <c r="F67" s="34" t="n"/>
@@ -16897,16 +16579,8 @@
       <c r="AK67" s="1" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="8" t="n"/>
       <c r="D68" s="1" t="n"/>
       <c r="E68" s="43" t="n"/>
       <c r="F68" s="34" t="n"/>
@@ -16942,16 +16616,8 @@
       <c r="AK68" s="1" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="8" t="n"/>
       <c r="D69" s="1" t="n"/>
       <c r="E69" s="43" t="n"/>
       <c r="F69" s="34" t="n"/>
@@ -16987,16 +16653,8 @@
       <c r="AK69" s="1" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="8" t="n"/>
       <c r="D70" s="1" t="n"/>
       <c r="E70" s="43" t="n"/>
       <c r="F70" s="34" t="n"/>
@@ -17032,16 +16690,8 @@
       <c r="AK70" s="1" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="8" t="n"/>
       <c r="D71" s="1" t="n"/>
       <c r="E71" s="43" t="n"/>
       <c r="F71" s="34" t="n"/>
@@ -17077,16 +16727,8 @@
       <c r="AK71" s="1" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="8" t="n"/>
       <c r="D72" s="1" t="n"/>
       <c r="E72" s="43" t="n"/>
       <c r="F72" s="34" t="n"/>
@@ -17122,16 +16764,8 @@
       <c r="AK72" s="1" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="8" t="n"/>
       <c r="D73" s="1" t="n"/>
       <c r="E73" s="43" t="n"/>
       <c r="F73" s="34" t="n"/>
@@ -17167,16 +16801,8 @@
       <c r="AK73" s="1" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="8" t="n"/>
       <c r="D74" s="1" t="n"/>
       <c r="E74" s="43" t="n"/>
       <c r="F74" s="34" t="n"/>
@@ -17212,16 +16838,8 @@
       <c r="AK74" s="1" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Feline 4</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="8" t="n"/>
       <c r="D75" s="1" t="n"/>
       <c r="E75" s="43" t="n"/>
       <c r="F75" s="34" t="n"/>
@@ -17257,16 +16875,7 @@
       <c r="AK75" s="1" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C76" s="1" t="n"/>
       <c r="D76" s="1" t="n"/>
       <c r="E76" s="43" t="n"/>
       <c r="F76" s="34" t="n"/>
@@ -17302,16 +16911,7 @@
       <c r="AK76" s="1" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C77" s="1" t="n"/>
       <c r="D77" s="1" t="n"/>
       <c r="E77" s="43" t="n"/>
       <c r="F77" s="34" t="n"/>
@@ -17347,16 +16947,7 @@
       <c r="AK77" s="1" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C78" s="1" t="n"/>
       <c r="D78" s="1" t="n"/>
       <c r="E78" s="43" t="n"/>
       <c r="F78" s="34" t="n"/>
@@ -17392,16 +16983,7 @@
       <c r="AK78" s="1" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C79" s="1" t="n"/>
       <c r="D79" s="1" t="n"/>
       <c r="E79" s="43" t="n"/>
       <c r="F79" s="34" t="n"/>
@@ -17437,16 +17019,7 @@
       <c r="AK79" s="1" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C80" s="1" t="n"/>
       <c r="D80" s="1" t="n"/>
       <c r="E80" s="43" t="n"/>
       <c r="F80" s="34" t="n"/>
@@ -17482,16 +17055,7 @@
       <c r="AK80" s="1" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C81" s="1" t="n"/>
       <c r="D81" s="1" t="n"/>
       <c r="E81" s="43" t="n"/>
       <c r="F81" s="34" t="n"/>
@@ -17527,16 +17091,7 @@
       <c r="AK81" s="1" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C82" s="1" t="n"/>
       <c r="D82" s="1" t="n"/>
       <c r="E82" s="43" t="n"/>
       <c r="F82" s="34" t="n"/>
@@ -17572,16 +17127,7 @@
       <c r="AK82" s="1" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C83" s="1" t="n"/>
       <c r="D83" s="1" t="n"/>
       <c r="E83" s="43" t="n"/>
       <c r="F83" s="34" t="n"/>
@@ -17617,16 +17163,7 @@
       <c r="AK83" s="1" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C84" s="1" t="n"/>
       <c r="D84" s="1" t="n"/>
       <c r="E84" s="43" t="n"/>
       <c r="F84" s="34" t="n"/>
@@ -17662,16 +17199,7 @@
       <c r="AK84" s="1" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Feline 5</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C85" s="1" t="n"/>
       <c r="D85" s="1" t="n"/>
       <c r="E85" s="43" t="n"/>
       <c r="F85" s="34" t="n"/>
@@ -17707,16 +17235,8 @@
       <c r="AK85" s="1" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="8" t="n"/>
       <c r="D86" s="1" t="n"/>
       <c r="E86" s="43" t="n"/>
       <c r="F86" s="34" t="n"/>
@@ -17752,16 +17272,8 @@
       <c r="AK86" s="1" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="8" t="n"/>
       <c r="D87" s="1" t="n"/>
       <c r="E87" s="43" t="n"/>
       <c r="F87" s="34" t="n"/>
@@ -17797,16 +17309,8 @@
       <c r="AK87" s="1" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="8" t="n"/>
       <c r="D88" s="1" t="n"/>
       <c r="E88" s="43" t="n"/>
       <c r="F88" s="34" t="n"/>
@@ -17842,16 +17346,8 @@
       <c r="AK88" s="1" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="8" t="n"/>
       <c r="D89" s="1" t="n"/>
       <c r="E89" s="43" t="n"/>
       <c r="F89" s="34" t="n"/>
@@ -17887,16 +17383,8 @@
       <c r="AK89" s="1" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="8" t="n"/>
       <c r="D90" s="1" t="n"/>
       <c r="E90" s="43" t="n"/>
       <c r="F90" s="34" t="n"/>
@@ -17932,16 +17420,8 @@
       <c r="AK90" s="1" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="8" t="n"/>
       <c r="D91" s="1" t="n"/>
       <c r="E91" s="43" t="n"/>
       <c r="F91" s="34" t="n"/>
@@ -17977,16 +17457,8 @@
       <c r="AK91" s="1" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="8" t="n"/>
       <c r="D92" s="1" t="n"/>
       <c r="E92" s="43" t="n"/>
       <c r="F92" s="34" t="n"/>
@@ -18022,16 +17494,8 @@
       <c r="AK92" s="1" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="8" t="n"/>
       <c r="D93" s="1" t="n"/>
       <c r="E93" s="43" t="n"/>
       <c r="F93" s="34" t="n"/>
@@ -18067,16 +17531,8 @@
       <c r="AK93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="8" t="n"/>
       <c r="D94" s="1" t="n"/>
       <c r="E94" s="43" t="n"/>
       <c r="F94" s="34" t="n"/>
@@ -18112,16 +17568,8 @@
       <c r="AK94" s="1" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Feline 6</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="8" t="n"/>
       <c r="D95" s="1" t="n"/>
       <c r="E95" s="43" t="n"/>
       <c r="F95" s="34" t="n"/>
@@ -19409,49 +18857,49 @@
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="43" t="inlineStr">
         <is>
-          <t>marker 1</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="43" t="inlineStr">
         <is>
-          <t>marker 2</t>
+          <t>AMY</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
       <c r="I3" s="43" t="inlineStr">
         <is>
-          <t>marker 3</t>
+          <t>CHOL</t>
         </is>
       </c>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="43" t="inlineStr">
         <is>
-          <t>marker 4</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="43" t="inlineStr">
         <is>
-          <t>marker 5</t>
+          <t>GLU</t>
         </is>
       </c>
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="43" t="inlineStr">
         <is>
-          <t>marker 6</t>
+          <t>P-LIPA</t>
         </is>
       </c>
       <c r="P3" s="3" t="n"/>
       <c r="Q3" s="43" t="inlineStr">
         <is>
-          <t>marker 7</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="R3" s="3" t="n"/>
       <c r="S3" s="43" t="inlineStr">
         <is>
-          <t>marker 8</t>
+          <t>TRIG</t>
         </is>
       </c>
       <c r="T3" s="3" t="n"/>
@@ -19470,42 +18918,42 @@
       <c r="Z3" s="1" t="n"/>
       <c r="AA3" s="1" t="inlineStr">
         <is>
-          <t>marker 1</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="AB3" s="1" t="inlineStr">
         <is>
-          <t>marker 2</t>
+          <t>AMY</t>
         </is>
       </c>
       <c r="AC3" s="1" t="inlineStr">
         <is>
-          <t>marker 3</t>
+          <t>CHOL</t>
         </is>
       </c>
       <c r="AD3" s="1" t="inlineStr">
         <is>
-          <t>marker 4</t>
+          <t>FRU</t>
         </is>
       </c>
       <c r="AE3" s="1" t="inlineStr">
         <is>
-          <t>marker 5</t>
+          <t>GLU</t>
         </is>
       </c>
       <c r="AF3" s="1" t="inlineStr">
         <is>
-          <t>marker 6</t>
+          <t>P-LIPA</t>
         </is>
       </c>
       <c r="AG3" s="1" t="inlineStr">
         <is>
-          <t>marker 7</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="AH3" s="1" t="inlineStr">
         <is>
-          <t>marker 8</t>
+          <t>TRIG</t>
         </is>
       </c>
       <c r="AI3" s="1" t="inlineStr">
@@ -19525,89 +18973,89 @@
       <c r="D4" s="29" t="n"/>
       <c r="E4" s="37" t="inlineStr">
         <is>
-          <t>marker 1(原線)</t>
+          <t>ALB(原線)</t>
         </is>
       </c>
       <c r="F4" s="30" t="inlineStr">
         <is>
-          <t>marker 1
+          <t>ALB
 換線後</t>
         </is>
       </c>
       <c r="G4" s="37" t="inlineStr">
         <is>
-          <t>marker 2(原線)</t>
+          <t>AMY(原線)</t>
         </is>
       </c>
       <c r="H4" s="30" t="inlineStr">
         <is>
-          <t>marker 2
+          <t>AMY
 換線後</t>
         </is>
       </c>
       <c r="I4" s="37" t="inlineStr">
         <is>
-          <t>marker 3(原線)</t>
+          <t>CHOL(原線)</t>
         </is>
       </c>
       <c r="J4" s="30" t="inlineStr">
         <is>
-          <t>marker 3
+          <t>CHOL
 換線後</t>
         </is>
       </c>
       <c r="K4" s="37" t="inlineStr">
         <is>
-          <t>marker 4(原線)</t>
+          <t>FRU(原線)</t>
         </is>
       </c>
       <c r="L4" s="30" t="inlineStr">
         <is>
-          <t>marker 4
+          <t>FRU
 換線後</t>
         </is>
       </c>
       <c r="M4" s="37" t="inlineStr">
         <is>
-          <t>marker 5(原線)</t>
+          <t>GLU(原線)</t>
         </is>
       </c>
       <c r="N4" s="30" t="inlineStr">
         <is>
-          <t>marker 5
+          <t>GLU
 換線後</t>
         </is>
       </c>
       <c r="O4" s="37" t="inlineStr">
         <is>
-          <t>marker 6(原線)</t>
+          <t>P-LIPA(原線)</t>
         </is>
       </c>
       <c r="P4" s="30" t="inlineStr">
         <is>
-          <t>marker 6
+          <t>P-LIPA
 換線後</t>
         </is>
       </c>
       <c r="Q4" s="37" t="inlineStr">
         <is>
-          <t>marker 7(原線)</t>
+          <t>TP(原線)</t>
         </is>
       </c>
       <c r="R4" s="30" t="inlineStr">
         <is>
-          <t>marker 7
+          <t>TP
 換線後</t>
         </is>
       </c>
       <c r="S4" s="37" t="inlineStr">
         <is>
-          <t>marker 8(原線)</t>
+          <t>TRIG(原線)</t>
         </is>
       </c>
       <c r="T4" s="30" t="inlineStr">
         <is>
-          <t>marker 8
+          <t>TRIG
 換線後</t>
         </is>
       </c>
@@ -20753,35 +20201,99 @@
         </is>
       </c>
       <c r="D34" s="1" t="n"/>
-      <c r="E34" s="43" t="n"/>
+      <c r="E34" s="43" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="43" t="n"/>
+      <c r="G34" s="43" t="inlineStr">
+        <is>
+          <t>AMY</t>
+        </is>
+      </c>
       <c r="H34" s="3" t="n"/>
-      <c r="I34" s="43" t="n"/>
+      <c r="I34" s="43" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
       <c r="J34" s="3" t="n"/>
-      <c r="K34" s="43" t="n"/>
+      <c r="K34" s="43" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
       <c r="L34" s="3" t="n"/>
-      <c r="M34" s="43" t="n"/>
+      <c r="M34" s="43" t="inlineStr">
+        <is>
+          <t>GLU</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="n"/>
-      <c r="O34" s="43" t="n"/>
+      <c r="O34" s="43" t="inlineStr">
+        <is>
+          <t>P-LIPA</t>
+        </is>
+      </c>
       <c r="P34" s="3" t="n"/>
-      <c r="Q34" s="43" t="n"/>
+      <c r="Q34" s="43" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
       <c r="R34" s="3" t="n"/>
-      <c r="S34" s="43" t="n"/>
+      <c r="S34" s="43" t="inlineStr">
+        <is>
+          <t>TRIG</t>
+        </is>
+      </c>
       <c r="T34" s="3" t="n"/>
       <c r="U34" s="43" t="n"/>
       <c r="V34" s="3" t="n"/>
       <c r="W34" s="43" t="n"/>
       <c r="X34" s="3" t="n"/>
       <c r="Z34" s="1" t="n"/>
-      <c r="AA34" s="1" t="n"/>
-      <c r="AB34" s="1" t="n"/>
-      <c r="AC34" s="1" t="n"/>
-      <c r="AD34" s="1" t="n"/>
-      <c r="AE34" s="1" t="n"/>
-      <c r="AF34" s="1" t="n"/>
-      <c r="AG34" s="1" t="n"/>
-      <c r="AH34" s="1" t="n"/>
+      <c r="AA34" s="1" t="inlineStr">
+        <is>
+          <t>ALB</t>
+        </is>
+      </c>
+      <c r="AB34" s="1" t="inlineStr">
+        <is>
+          <t>AMY</t>
+        </is>
+      </c>
+      <c r="AC34" s="1" t="inlineStr">
+        <is>
+          <t>CHOL</t>
+        </is>
+      </c>
+      <c r="AD34" s="1" t="inlineStr">
+        <is>
+          <t>FRU</t>
+        </is>
+      </c>
+      <c r="AE34" s="1" t="inlineStr">
+        <is>
+          <t>GLU</t>
+        </is>
+      </c>
+      <c r="AF34" s="1" t="inlineStr">
+        <is>
+          <t>P-LIPA</t>
+        </is>
+      </c>
+      <c r="AG34" s="1" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="AH34" s="1" t="inlineStr">
+        <is>
+          <t>TRIG</t>
+        </is>
+      </c>
       <c r="AI34" s="1" t="n"/>
       <c r="AJ34" s="1" t="n"/>
       <c r="AK34" s="13" t="inlineStr">
@@ -20793,22 +20305,94 @@
     <row r="35" ht="33" customHeight="1">
       <c r="C35" s="11" t="n"/>
       <c r="D35" s="1" t="n"/>
-      <c r="E35" s="37" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="37" t="n"/>
-      <c r="H35" s="30" t="n"/>
-      <c r="I35" s="37" t="n"/>
-      <c r="J35" s="30" t="n"/>
-      <c r="K35" s="37" t="n"/>
-      <c r="L35" s="30" t="n"/>
-      <c r="M35" s="37" t="n"/>
-      <c r="N35" s="30" t="n"/>
-      <c r="O35" s="37" t="n"/>
-      <c r="P35" s="30" t="n"/>
-      <c r="Q35" s="37" t="n"/>
-      <c r="R35" s="30" t="n"/>
-      <c r="S35" s="37" t="n"/>
-      <c r="T35" s="30" t="n"/>
+      <c r="E35" s="37" t="inlineStr">
+        <is>
+          <t>ALB(原線)</t>
+        </is>
+      </c>
+      <c r="F35" s="30" t="inlineStr">
+        <is>
+          <t>ALB
+換線後</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="inlineStr">
+        <is>
+          <t>AMY(原線)</t>
+        </is>
+      </c>
+      <c r="H35" s="30" t="inlineStr">
+        <is>
+          <t>AMY
+換線後</t>
+        </is>
+      </c>
+      <c r="I35" s="37" t="inlineStr">
+        <is>
+          <t>CHOL(原線)</t>
+        </is>
+      </c>
+      <c r="J35" s="30" t="inlineStr">
+        <is>
+          <t>CHOL
+換線後</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="inlineStr">
+        <is>
+          <t>FRU(原線)</t>
+        </is>
+      </c>
+      <c r="L35" s="30" t="inlineStr">
+        <is>
+          <t>FRU
+換線後</t>
+        </is>
+      </c>
+      <c r="M35" s="37" t="inlineStr">
+        <is>
+          <t>GLU(原線)</t>
+        </is>
+      </c>
+      <c r="N35" s="30" t="inlineStr">
+        <is>
+          <t>GLU
+換線後</t>
+        </is>
+      </c>
+      <c r="O35" s="37" t="inlineStr">
+        <is>
+          <t>P-LIPA(原線)</t>
+        </is>
+      </c>
+      <c r="P35" s="30" t="inlineStr">
+        <is>
+          <t>P-LIPA
+換線後</t>
+        </is>
+      </c>
+      <c r="Q35" s="37" t="inlineStr">
+        <is>
+          <t>TP(原線)</t>
+        </is>
+      </c>
+      <c r="R35" s="30" t="inlineStr">
+        <is>
+          <t>TP
+換線後</t>
+        </is>
+      </c>
+      <c r="S35" s="37" t="inlineStr">
+        <is>
+          <t>TRIG(原線)</t>
+        </is>
+      </c>
+      <c r="T35" s="30" t="inlineStr">
+        <is>
+          <t>TRIG
+換線後</t>
+        </is>
+      </c>
       <c r="U35" s="37" t="n"/>
       <c r="V35" s="30" t="n"/>
       <c r="W35" s="37" t="n"/>
@@ -20827,16 +20411,7 @@
       <c r="AK35" s="13" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C36" s="1" t="n"/>
       <c r="D36" s="1" t="n"/>
       <c r="E36" s="43" t="n"/>
       <c r="F36" s="34" t="n"/>
@@ -20872,16 +20447,7 @@
       <c r="AK36" s="1" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C37" s="1" t="n"/>
       <c r="D37" s="1" t="n"/>
       <c r="E37" s="43" t="n"/>
       <c r="F37" s="34" t="n"/>
@@ -20917,16 +20483,7 @@
       <c r="AK37" s="1" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C38" s="1" t="n"/>
       <c r="D38" s="1" t="n"/>
       <c r="E38" s="43" t="n"/>
       <c r="F38" s="34" t="n"/>
@@ -20962,16 +20519,7 @@
       <c r="AK38" s="1" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C39" s="1" t="n"/>
       <c r="D39" s="1" t="n"/>
       <c r="E39" s="43" t="n"/>
       <c r="F39" s="34" t="n"/>
@@ -21007,16 +20555,7 @@
       <c r="AK39" s="1" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C40" s="1" t="n"/>
       <c r="D40" s="1" t="n"/>
       <c r="E40" s="43" t="n"/>
       <c r="F40" s="34" t="n"/>
@@ -21052,16 +20591,7 @@
       <c r="AK40" s="1" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C41" s="1" t="n"/>
       <c r="D41" s="1" t="n"/>
       <c r="E41" s="43" t="n"/>
       <c r="F41" s="34" t="n"/>
@@ -21097,16 +20627,7 @@
       <c r="AK41" s="1" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C42" s="1" t="n"/>
       <c r="D42" s="1" t="n"/>
       <c r="E42" s="43" t="n"/>
       <c r="F42" s="34" t="n"/>
@@ -21142,16 +20663,7 @@
       <c r="AK42" s="1" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C43" s="1" t="n"/>
       <c r="D43" s="1" t="n"/>
       <c r="E43" s="43" t="n"/>
       <c r="F43" s="34" t="n"/>
@@ -21187,16 +20699,7 @@
       <c r="AK43" s="1" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C44" s="1" t="n"/>
       <c r="D44" s="1" t="n"/>
       <c r="E44" s="43" t="n"/>
       <c r="F44" s="34" t="n"/>
@@ -21232,16 +20735,7 @@
       <c r="AK44" s="1" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Equine 1</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C45" s="1" t="n"/>
       <c r="D45" s="1" t="n"/>
       <c r="E45" s="43" t="n"/>
       <c r="F45" s="34" t="n"/>
@@ -21277,16 +20771,8 @@
       <c r="AK45" s="1" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="8" t="n"/>
       <c r="D46" s="1" t="n"/>
       <c r="E46" s="43" t="n"/>
       <c r="F46" s="34" t="n"/>
@@ -21322,16 +20808,8 @@
       <c r="AK46" s="1" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="8" t="n"/>
       <c r="D47" s="1" t="n"/>
       <c r="E47" s="43" t="n"/>
       <c r="F47" s="34" t="n"/>
@@ -21367,16 +20845,8 @@
       <c r="AK47" s="1" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="8" t="n"/>
       <c r="D48" s="1" t="n"/>
       <c r="E48" s="43" t="n"/>
       <c r="F48" s="34" t="n"/>
@@ -21412,16 +20882,8 @@
       <c r="AK48" s="1" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="8" t="n"/>
       <c r="D49" s="1" t="n"/>
       <c r="E49" s="43" t="n"/>
       <c r="F49" s="34" t="n"/>
@@ -21457,16 +20919,8 @@
       <c r="AK49" s="1" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="8" t="n"/>
       <c r="D50" s="1" t="n"/>
       <c r="E50" s="43" t="n"/>
       <c r="F50" s="34" t="n"/>
@@ -21502,16 +20956,8 @@
       <c r="AK50" s="1" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="8" t="n"/>
       <c r="D51" s="1" t="n"/>
       <c r="E51" s="43" t="n"/>
       <c r="F51" s="34" t="n"/>
@@ -21547,16 +20993,8 @@
       <c r="AK51" s="1" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="8" t="n"/>
       <c r="D52" s="1" t="n"/>
       <c r="E52" s="43" t="n"/>
       <c r="F52" s="34" t="n"/>
@@ -21592,16 +21030,8 @@
       <c r="AK52" s="1" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="8" t="n"/>
       <c r="D53" s="1" t="n"/>
       <c r="E53" s="43" t="n"/>
       <c r="F53" s="34" t="n"/>
@@ -21637,16 +21067,8 @@
       <c r="AK53" s="1" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="8" t="n"/>
       <c r="D54" s="1" t="n"/>
       <c r="E54" s="43" t="n"/>
       <c r="F54" s="34" t="n"/>
@@ -21682,16 +21104,8 @@
       <c r="AK54" s="1" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>Equine 2</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="8" t="n"/>
       <c r="D55" s="1" t="n"/>
       <c r="E55" s="43" t="n"/>
       <c r="F55" s="34" t="n"/>
@@ -21727,16 +21141,7 @@
       <c r="AK55" s="1" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C56" s="1" t="n"/>
       <c r="D56" s="1" t="n"/>
       <c r="E56" s="43" t="n"/>
       <c r="F56" s="34" t="n"/>
@@ -21772,16 +21177,7 @@
       <c r="AK56" s="1" t="n"/>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C57" s="1" t="n"/>
       <c r="D57" s="1" t="n"/>
       <c r="E57" s="43" t="n"/>
       <c r="F57" s="34" t="n"/>
@@ -21817,16 +21213,7 @@
       <c r="AK57" s="1" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C58" s="1" t="n"/>
       <c r="D58" s="1" t="n"/>
       <c r="E58" s="43" t="n"/>
       <c r="F58" s="34" t="n"/>
@@ -21862,16 +21249,7 @@
       <c r="AK58" s="1" t="n"/>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C59" s="1" t="n"/>
       <c r="D59" s="1" t="n"/>
       <c r="E59" s="43" t="n"/>
       <c r="F59" s="34" t="n"/>
@@ -21907,16 +21285,7 @@
       <c r="AK59" s="1" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C60" s="1" t="n"/>
       <c r="D60" s="1" t="n"/>
       <c r="E60" s="43" t="n"/>
       <c r="F60" s="34" t="n"/>
@@ -21952,16 +21321,7 @@
       <c r="AK60" s="1" t="n"/>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C61" s="1" t="n"/>
       <c r="D61" s="1" t="n"/>
       <c r="E61" s="43" t="n"/>
       <c r="F61" s="34" t="n"/>
@@ -21997,16 +21357,7 @@
       <c r="AK61" s="1" t="n"/>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C62" s="1" t="n"/>
       <c r="D62" s="1" t="n"/>
       <c r="E62" s="43" t="n"/>
       <c r="F62" s="34" t="n"/>
@@ -22042,16 +21393,7 @@
       <c r="AK62" s="1" t="n"/>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C63" s="1" t="n"/>
       <c r="D63" s="1" t="n"/>
       <c r="E63" s="43" t="n"/>
       <c r="F63" s="34" t="n"/>
@@ -22087,16 +21429,7 @@
       <c r="AK63" s="1" t="n"/>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C64" s="1" t="n"/>
       <c r="D64" s="1" t="n"/>
       <c r="E64" s="43" t="n"/>
       <c r="F64" s="34" t="n"/>
@@ -22132,16 +21465,7 @@
       <c r="AK64" s="1" t="n"/>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Equine 3</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C65" s="1" t="n"/>
       <c r="D65" s="1" t="n"/>
       <c r="E65" s="43" t="n"/>
       <c r="F65" s="34" t="n"/>
@@ -22177,16 +21501,8 @@
       <c r="AK65" s="1" t="n"/>
     </row>
     <row r="66">
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="8" t="n"/>
       <c r="D66" s="1" t="n"/>
       <c r="E66" s="43" t="n"/>
       <c r="F66" s="34" t="n"/>
@@ -22222,16 +21538,8 @@
       <c r="AK66" s="1" t="n"/>
     </row>
     <row r="67">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B67" s="6" t="n"/>
+      <c r="C67" s="8" t="n"/>
       <c r="D67" s="1" t="n"/>
       <c r="E67" s="43" t="n"/>
       <c r="F67" s="34" t="n"/>
@@ -22267,16 +21575,8 @@
       <c r="AK67" s="1" t="n"/>
     </row>
     <row r="68">
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="8" t="n"/>
       <c r="D68" s="1" t="n"/>
       <c r="E68" s="43" t="n"/>
       <c r="F68" s="34" t="n"/>
@@ -22312,16 +21612,8 @@
       <c r="AK68" s="1" t="n"/>
     </row>
     <row r="69">
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="8" t="n"/>
       <c r="D69" s="1" t="n"/>
       <c r="E69" s="43" t="n"/>
       <c r="F69" s="34" t="n"/>
@@ -22357,16 +21649,8 @@
       <c r="AK69" s="1" t="n"/>
     </row>
     <row r="70">
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="8" t="n"/>
       <c r="D70" s="1" t="n"/>
       <c r="E70" s="43" t="n"/>
       <c r="F70" s="34" t="n"/>
@@ -22402,16 +21686,8 @@
       <c r="AK70" s="1" t="n"/>
     </row>
     <row r="71">
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="8" t="n"/>
       <c r="D71" s="1" t="n"/>
       <c r="E71" s="43" t="n"/>
       <c r="F71" s="34" t="n"/>
@@ -22447,16 +21723,8 @@
       <c r="AK71" s="1" t="n"/>
     </row>
     <row r="72">
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C72" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="8" t="n"/>
       <c r="D72" s="1" t="n"/>
       <c r="E72" s="43" t="n"/>
       <c r="F72" s="34" t="n"/>
@@ -22492,16 +21760,8 @@
       <c r="AK72" s="1" t="n"/>
     </row>
     <row r="73">
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="8" t="n"/>
       <c r="D73" s="1" t="n"/>
       <c r="E73" s="43" t="n"/>
       <c r="F73" s="34" t="n"/>
@@ -22537,16 +21797,8 @@
       <c r="AK73" s="1" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B74" s="6" t="n"/>
+      <c r="C74" s="8" t="n"/>
       <c r="D74" s="1" t="n"/>
       <c r="E74" s="43" t="n"/>
       <c r="F74" s="34" t="n"/>
@@ -22582,16 +21834,8 @@
       <c r="AK74" s="1" t="n"/>
     </row>
     <row r="75">
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>Equine 4</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="8" t="n"/>
       <c r="D75" s="1" t="n"/>
       <c r="E75" s="43" t="n"/>
       <c r="F75" s="34" t="n"/>
@@ -22627,16 +21871,7 @@
       <c r="AK75" s="1" t="n"/>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C76" s="1" t="n"/>
       <c r="D76" s="1" t="n"/>
       <c r="E76" s="43" t="n"/>
       <c r="F76" s="34" t="n"/>
@@ -22672,16 +21907,7 @@
       <c r="AK76" s="1" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C77" s="1" t="n"/>
       <c r="D77" s="1" t="n"/>
       <c r="E77" s="43" t="n"/>
       <c r="F77" s="34" t="n"/>
@@ -22717,16 +21943,7 @@
       <c r="AK77" s="1" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C78" s="1" t="n"/>
       <c r="D78" s="1" t="n"/>
       <c r="E78" s="43" t="n"/>
       <c r="F78" s="34" t="n"/>
@@ -22762,16 +21979,7 @@
       <c r="AK78" s="1" t="n"/>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C79" s="1" t="n"/>
       <c r="D79" s="1" t="n"/>
       <c r="E79" s="43" t="n"/>
       <c r="F79" s="34" t="n"/>
@@ -22807,16 +22015,7 @@
       <c r="AK79" s="1" t="n"/>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C80" s="1" t="n"/>
       <c r="D80" s="1" t="n"/>
       <c r="E80" s="43" t="n"/>
       <c r="F80" s="34" t="n"/>
@@ -22852,16 +22051,7 @@
       <c r="AK80" s="1" t="n"/>
     </row>
     <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C81" s="1" t="n"/>
       <c r="D81" s="1" t="n"/>
       <c r="E81" s="43" t="n"/>
       <c r="F81" s="34" t="n"/>
@@ -22897,16 +22087,7 @@
       <c r="AK81" s="1" t="n"/>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C82" s="1" t="n"/>
       <c r="D82" s="1" t="n"/>
       <c r="E82" s="43" t="n"/>
       <c r="F82" s="34" t="n"/>
@@ -22942,16 +22123,7 @@
       <c r="AK82" s="1" t="n"/>
     </row>
     <row r="83">
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C83" s="1" t="n"/>
       <c r="D83" s="1" t="n"/>
       <c r="E83" s="43" t="n"/>
       <c r="F83" s="34" t="n"/>
@@ -22987,16 +22159,7 @@
       <c r="AK83" s="1" t="n"/>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C84" s="1" t="n"/>
       <c r="D84" s="1" t="n"/>
       <c r="E84" s="43" t="n"/>
       <c r="F84" s="34" t="n"/>
@@ -23032,16 +22195,7 @@
       <c r="AK84" s="1" t="n"/>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Equine 5</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="C85" s="1" t="n"/>
       <c r="D85" s="1" t="n"/>
       <c r="E85" s="43" t="n"/>
       <c r="F85" s="34" t="n"/>
@@ -23077,16 +22231,8 @@
       <c r="AK85" s="1" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B86" s="6" t="n"/>
+      <c r="C86" s="8" t="n"/>
       <c r="D86" s="1" t="n"/>
       <c r="E86" s="43" t="n"/>
       <c r="F86" s="34" t="n"/>
@@ -23122,16 +22268,8 @@
       <c r="AK86" s="1" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B87" s="6" t="n"/>
+      <c r="C87" s="8" t="n"/>
       <c r="D87" s="1" t="n"/>
       <c r="E87" s="43" t="n"/>
       <c r="F87" s="34" t="n"/>
@@ -23167,16 +22305,8 @@
       <c r="AK87" s="1" t="n"/>
     </row>
     <row r="88">
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="8" t="n"/>
       <c r="D88" s="1" t="n"/>
       <c r="E88" s="43" t="n"/>
       <c r="F88" s="34" t="n"/>
@@ -23212,16 +22342,8 @@
       <c r="AK88" s="1" t="n"/>
     </row>
     <row r="89">
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="8" t="n"/>
       <c r="D89" s="1" t="n"/>
       <c r="E89" s="43" t="n"/>
       <c r="F89" s="34" t="n"/>
@@ -23257,16 +22379,8 @@
       <c r="AK89" s="1" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="8" t="n"/>
       <c r="D90" s="1" t="n"/>
       <c r="E90" s="43" t="n"/>
       <c r="F90" s="34" t="n"/>
@@ -23302,16 +22416,8 @@
       <c r="AK90" s="1" t="n"/>
     </row>
     <row r="91">
-      <c r="B91" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="8" t="n"/>
       <c r="D91" s="1" t="n"/>
       <c r="E91" s="43" t="n"/>
       <c r="F91" s="34" t="n"/>
@@ -23347,16 +22453,8 @@
       <c r="AK91" s="1" t="n"/>
     </row>
     <row r="92">
-      <c r="B92" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="8" t="n"/>
       <c r="D92" s="1" t="n"/>
       <c r="E92" s="43" t="n"/>
       <c r="F92" s="34" t="n"/>
@@ -23392,16 +22490,8 @@
       <c r="AK92" s="1" t="n"/>
     </row>
     <row r="93">
-      <c r="B93" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="8" t="n"/>
       <c r="D93" s="1" t="n"/>
       <c r="E93" s="43" t="n"/>
       <c r="F93" s="34" t="n"/>
@@ -23437,16 +22527,8 @@
       <c r="AK93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C94" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="8" t="n"/>
       <c r="D94" s="1" t="n"/>
       <c r="E94" s="43" t="n"/>
       <c r="F94" s="34" t="n"/>
@@ -23482,16 +22564,8 @@
       <c r="AK94" s="1" t="n"/>
     </row>
     <row r="95">
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>Equine 6</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>機台序號3</t>
-        </is>
-      </c>
+      <c r="B95" s="6" t="n"/>
+      <c r="C95" s="8" t="n"/>
       <c r="D95" s="1" t="n"/>
       <c r="E95" s="43" t="n"/>
       <c r="F95" s="34" t="n"/>
